--- a/Mataquito/supplemental/Table_S6.xlsx
+++ b/Mataquito/supplemental/Table_S6.xlsx
@@ -1,76 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Glong1/Desktop/Andes/Chapter_1_Manuscript/LaTex Files/overleaf/files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA217AE7-F74F-1944-B684-EFCB149CC50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S6" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
-  <si>
-    <t>Parents</t>
-  </si>
-  <si>
-    <t>CT-10</t>
-  </si>
-  <si>
-    <t>CT-11</t>
-  </si>
-  <si>
-    <t>CT-8.2</t>
-  </si>
-  <si>
-    <t>CT-2</t>
-  </si>
-  <si>
-    <t>CT-9</t>
-  </si>
-  <si>
-    <t>CT-5</t>
-  </si>
-  <si>
-    <t>CT-6</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>CT-3</t>
-  </si>
-  <si>
-    <t>Children</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -89,24 +47,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -394,232 +411,546 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="8.5" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>0.66400000000000003</v>
-      </c>
-      <c r="C3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Best-fit mixing coefficients, V_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Children</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Parents</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CT-10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CT-11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CT-8.2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CT-2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CT-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CT-5</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.495</v>
       </c>
-      <c r="D3">
-        <v>0.55900000000000005</v>
-      </c>
-      <c r="E3">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="F3">
-        <v>0.28100000000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>0.33600000000000002</v>
-      </c>
-      <c r="C4">
+      <c r="D4" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.719</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CT-6</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.505</v>
       </c>
-      <c r="D4">
+      <c r="D5" t="n">
         <v>0.441</v>
       </c>
-      <c r="E4">
-        <v>0.79400000000000004</v>
-      </c>
-      <c r="F4">
-        <v>0.71899999999999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6">
+      <c r="E5" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.281</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CT-10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>0.79</v>
       </c>
-      <c r="F6">
-        <v>0.88100000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7">
+      <c r="F7" t="n">
+        <v>0.881</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CT-3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>0.21</v>
       </c>
-      <c r="F7">
-        <v>0.11899999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9">
-        <v>0.88100000000000001</v>
-      </c>
-      <c r="F9">
+      <c r="F8" t="n">
+        <v>0.119</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CT-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.86</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="F10">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12">
-        <v>0.81</v>
-      </c>
-      <c r="F12">
-        <v>0.83099999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CT-3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CT-8.2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.831</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CT-3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>0.19</v>
       </c>
-      <c r="F13">
-        <v>0.16900000000000001</v>
+      <c r="F14" t="n">
+        <v>0.169</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Best-fit mixing coefficients, r2-KDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Children</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Parents</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CT-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CT-11</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CT-8.2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CT-2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CT-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CT-5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CT-6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CT-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.945</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CT-3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CT-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CT-3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CT-8.2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.954</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CT-3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.046</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A5:F5"/>
+  <mergeCells count="8">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
